--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260608.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>6,921,000</t>
+          <t>7,631,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>7,631,000</t>
+          <t>6,921,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
